--- a/static/standards-correlations/Missouri_CS1_State_Standards.xlsx
+++ b/static/standards-correlations/Missouri_CS1_State_Standards.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Crosswalk" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Legend &amp; Attribution" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Crosswalk" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Legend &amp; Attribution" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Crosswalk'!$A$4:$I$40</definedName>
@@ -550,10 +550,11 @@
     <row r="2" ht="18" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Scored against full lab bodies | C and Python tracks | Discovery Projects | Missouri K-12 CS Standards, enacted 2019</t>
-        </is>
-      </c>
-    </row>
+          <t>Scored against full lab bodies | C and Python tracks | Introductory Projects | Missouri K-12 CS Standards, enacted 2019</t>
+        </is>
+      </c>
+    </row>
+    <row r="3"/>
     <row r="4" ht="32" customHeight="1">
       <c r="A4" s="3" t="inlineStr">
         <is>
@@ -587,7 +588,7 @@
       </c>
       <c r="G4" s="3" t="inlineStr">
         <is>
-          <t>Discovery Projects</t>
+          <t>Introductory Projects</t>
         </is>
       </c>
       <c r="H4" s="3" t="inlineStr">
@@ -785,7 +786,7 @@
       </c>
       <c r="I8" s="8" t="inlineStr">
         <is>
-          <t>Ext 5.3F (Talking to a Server) introduces the server as a distinct role and Discovery Systems 9 covers protocols. Routers, switches, IP, and DNS are absent.</t>
+          <t>Ext 5.3F (Talking to a Server) introduces the server as a distinct role and Introductory Systems 9 covers protocols. Routers, switches, IP, and DNS are absent.</t>
         </is>
       </c>
     </row>
@@ -926,7 +927,7 @@
       </c>
       <c r="I11" s="8" t="inlineStr">
         <is>
-          <t>Ext 5.3G (Secret Messages / HTTPS) shows a credential exposed in transit over HTTP; Discovery Systems 10 covers phishing.</t>
+          <t>Ext 5.3G (Secret Messages / HTTPS) shows a credential exposed in transit over HTTP; Introductory Systems 10 covers phishing.</t>
         </is>
       </c>
     </row>
@@ -1658,7 +1659,7 @@
       </c>
       <c r="I27" s="5" t="inlineStr">
         <is>
-          <t>Discovery Systems 4 teaches flowchart symbols, Ext 1.2B (Dependency Map) produces a node-and-arrow structure diagram, and Ext 5.1G (Write the Guide) plus Ext 5.3A (Write a Real README) supply the documentation.</t>
+          <t>Introductory Systems 4 teaches flowchart symbols, Ext 1.2B (Dependency Map) produces a node-and-arrow structure diagram, and Ext 5.1G (Write the Guide) plus Ext 5.3A (Write a Real README) supply the documentation.</t>
         </is>
       </c>
     </row>
@@ -1752,7 +1753,7 @@
       </c>
       <c r="I29" s="5" t="inlineStr">
         <is>
-          <t>Botball Explorer is team-based by design. Unit 5.3 adds shared repositories and Discovery Systems 13 assigns rotating roles.</t>
+          <t>Botball Explorer is team-based by design. Unit 5.3 adds shared repositories and Introductory Systems 13 assigns rotating roles.</t>
         </is>
       </c>
     </row>
@@ -2069,7 +2070,7 @@
       </c>
       <c r="I36" s="8" t="inlineStr">
         <is>
-          <t>Discovery Coding 2 addresses how professional programmers spend their time and Ext 5.3H (Find the Community) exposes students to practitioner collaboration. Career-field impact is not analysed.</t>
+          <t>Introductory Coding 2 addresses how professional programmers spend their time and Ext 5.3H (Find the Community) exposes students to practitioner collaboration. Career-field impact is not analysed.</t>
         </is>
       </c>
     </row>
@@ -2287,6 +2288,7 @@
         </is>
       </c>
     </row>
+    <row r="2"/>
     <row r="3">
       <c r="A3" s="11" t="inlineStr">
         <is>
@@ -2331,7 +2333,7 @@
       </c>
       <c r="B6" s="12" t="inlineStr">
         <is>
-          <t>Discovery Project, Coding strand, project NN (01-17).</t>
+          <t>Introductory Project, Coding strand, project NN (01-17).</t>
         </is>
       </c>
     </row>
@@ -2343,7 +2345,7 @@
       </c>
       <c r="B7" s="12" t="inlineStr">
         <is>
-          <t>Discovery Project, Systems strand, project NN (01-14).</t>
+          <t>Introductory Project, Systems strand, project NN (01-14).</t>
         </is>
       </c>
     </row>
@@ -2443,6 +2445,8 @@
         </is>
       </c>
     </row>
+    <row r="16"/>
+    <row r="17"/>
     <row r="18">
       <c r="A18" s="10" t="inlineStr">
         <is>
@@ -2460,7 +2464,7 @@
 SOURCE NOTE: Standard codes and statements were transcribed from the CodeHS published Missouri 9-10 standards framework. The 2019 enactment and the mathematics-credit provision were verified against Missouri DESE reporting. Verify wording against the official DESE standards document before using this crosswalk in any formal submission.
 Crosswalk analysis (c) KIPR / Botball Explorer.
 === METHODOLOGY (revised) ===
-Scored against FULL LAB BODIES: reflection prompts, Individual Reflection phases, AI Literacy Bridge sections, and Extension Challenges. Evidence base is 750 reflection prompts and 255 Extension Challenges across 27 C labs, 27 Python labs, and 31 Discovery projects.
+Scored against FULL LAB BODIES: reflection prompts, Individual Reflection phases, AI Literacy Bridge sections, and Extension Challenges. Evidence base is 750 reflection prompts and 255 Extension Challenges across 27 C labs, 27 Python labs, and 31 Introductory projects.
 Scoring rule: Full requires evidence in the core lab flow. Partial is assigned where the only evidence sits in an optional Extension Challenge (labelled 'Finished early?'), or where the standard is only partly met.</t>
         </is>
       </c>
